--- a/Result/profitability/6196.xlsx
+++ b/Result/profitability/6196.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.14</v>
       </c>
       <c r="M2" t="n">
-        <v>3.18875</v>
+        <v>3.875</v>
       </c>
       <c r="N2" t="n">
-        <v>11.89875</v>
+        <v>12.38125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.47</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9125</v>
+        <v>3.68375</v>
       </c>
       <c r="N3" t="n">
-        <v>11.8225</v>
+        <v>12.21</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.54</v>
       </c>
       <c r="M4" t="n">
-        <v>2.73</v>
+        <v>3.2</v>
       </c>
       <c r="N4" t="n">
-        <v>12.0325</v>
+        <v>12.33625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.28</v>
       </c>
       <c r="M5" t="n">
-        <v>2.21375</v>
+        <v>2.99125</v>
       </c>
       <c r="N5" t="n">
-        <v>11.98375</v>
+        <v>12.245</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>1.99125</v>
+        <v>2.31625</v>
       </c>
       <c r="N6" t="n">
-        <v>12.405</v>
+        <v>12.71125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.12</v>
       </c>
       <c r="M7" t="n">
-        <v>1.28</v>
+        <v>1.84125</v>
       </c>
       <c r="N7" t="n">
-        <v>13.16125</v>
+        <v>13.52375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0.76375</v>
+        <v>1.15</v>
       </c>
       <c r="N8" t="n">
-        <v>13.4075</v>
+        <v>13.3925</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>21200</v>
+      </c>
+      <c r="D75" t="n">
+        <v>18348</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2852</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1892</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.92%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>320</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2212</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1801</v>
+      </c>
+      <c r="L75" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="M75" t="n">
+        <v>4.1925</v>
+      </c>
+      <c r="N75" t="n">
+        <v>11.36125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6082677165354331</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.120000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.008843036109064228</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>3.18974358974359</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1839788732394365</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
